--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR TEMPARATURA OLEO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR TEMPARATURA OLEO.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SENSOR TEMP OLEO IRON YS250 FAZER 2006 A 2023/ XTZ250 LANDER 2008 A 2023/ TENERE 352233</t>
+          <t>SENSOR TEMPERATURA  OLEO IRON YS250 FAZER 2006 A 2023/ XTZ250 LANDER 2008 A 2023/ TENERE 352233</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +457,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SENSOR TEMP OLEO IRON CONDOR NEO115</t>
+          <t>SENSOR TEMPERATURA  OLEO IRON CONDOR NEO115</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -495,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SENSOR TEMP OLEO MHX CG TITAN150 2009 A 2015/ FAN160 2016 A 2022/ CACTO150 2016 A 2022/ NMAX160 2017 A 2022/ XRE300 2009 A 2022/ BIZ125/ XRE190</t>
+          <t>SENSOR TEMPERATURA  OLEO MHX CG TITAN150 2009 A 2015/ FAN160 2016 A 2022/ CACTO150 2016 A 2022/ NMAX160 2017 A 2022/ XRE300 2009 A 2022/ BIZ125/ XRE190</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -503,7 +507,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -516,11 +524,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SENSOR TEMP OLEO IRON FAZER YS150 250 2014 A 2024/ XTZ150 CROSSER 2015 A 2023/ YBR125I 2017 A 2023/ FACTOR150 2016 A 2023 352235</t>
+          <t>SENSOR TEMPERATURA  OLEO IRON FAZER YS150 250 2014 A 2024/ XTZ150 CROSSER 2015 A 2023/ YBR125I 2017 A 2023/ FACTOR150 2016 A 2023 352235</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR TEMPARATURA OLEO.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/SENSOR TEMPARATURA OLEO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,11 +508,6 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
